--- a/data/trans_camb/IP43-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP43-Habitat-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-21,1; -4,68</t>
+          <t>-21,82; -4,35</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-36,5; -23,64</t>
+          <t>-36,39; -23,16</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-22,67; -5,8</t>
+          <t>-22,77; -6,73</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-37,53; -25,0</t>
+          <t>-37,03; -24,46</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-19,4; -7,94</t>
+          <t>-19,73; -8,23</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-34,86; -25,63</t>
+          <t>-34,6; -25,32</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-63,23; -16,4</t>
+          <t>-64,27; -17,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-64,2; -21,17</t>
+          <t>-65,18; -21,83</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-58,67; -30,01</t>
+          <t>-58,85; -29,11</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-20,81; -8,02</t>
+          <t>-20,85; -7,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-36,53; -26,68</t>
+          <t>-36,63; -26,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-22,47; -9,63</t>
+          <t>-22,81; -9,35</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-38,63; -28,39</t>
+          <t>-38,13; -28,12</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-19,69; -10,52</t>
+          <t>-20,13; -10,38</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-36,05; -29,4</t>
+          <t>-36,2; -29,06</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-59,22; -27,11</t>
+          <t>-59,55; -26,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-60,55; -32,3</t>
+          <t>-60,62; -29,55</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-56,25; -34,59</t>
+          <t>-56,36; -33,54</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-15,39; -4,56</t>
+          <t>-15,76; -4,7</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-21,34; -12,25</t>
+          <t>-21,76; -12,59</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-16,56; -5,77</t>
+          <t>-16,38; -5,76</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-21,41; -12,45</t>
+          <t>-21,27; -12,27</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-14,37; -6,44</t>
+          <t>-14,14; -6,16</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-20,08; -13,71</t>
+          <t>-19,69; -13,13</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-75,16; -33,55</t>
+          <t>-76,44; -33,29</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-81,2; -36,08</t>
+          <t>-83,29; -40,03</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-75,26; -44,98</t>
+          <t>-74,83; -44,78</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-10,67; -0,05</t>
+          <t>-10,68; 0,05</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-19,16; -10,78</t>
+          <t>-18,89; -10,41</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-11,09; -1,19</t>
+          <t>-10,93; -1,09</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-16,89; -9,18</t>
+          <t>-17,01; -9,17</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-9,54; -1,93</t>
+          <t>-9,26; -2,33</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-16,68; -10,82</t>
+          <t>-16,76; -11,04</t>
         </is>
       </c>
     </row>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-59,49; 0,5</t>
+          <t>-59,36; 1,73</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-71,24; -10,31</t>
+          <t>-70,71; -11,03</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-59,95; -16,28</t>
+          <t>-59,6; -18,97</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-13,53; -7,09</t>
+          <t>-14,03; -7,35</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-25,82; -20,59</t>
+          <t>-25,51; -20,6</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-15,07; -8,97</t>
+          <t>-15,34; -8,64</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-26,06; -20,77</t>
+          <t>-25,83; -20,87</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-13,5; -8,86</t>
+          <t>-13,29; -8,84</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-24,85; -21,13</t>
+          <t>-24,95; -21,47</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-55,03; -34,58</t>
+          <t>-56,01; -34,47</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-59,6; -41,59</t>
+          <t>-60,1; -40,06</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-55,23; -40,91</t>
+          <t>-55,25; -40,38</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
